--- a/estimate_scenarios.xlsx
+++ b/estimate_scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\v-minasyanva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320E8621-AE04-4E03-966E-CFA3DCFFEB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30700167-AB41-4F56-BFE8-CF7DA68F6E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{8CC6B35D-15F8-46B2-8EDB-45E5A707818B}"/>
+    <workbookView xWindow="38505" yWindow="2565" windowWidth="24630" windowHeight="16680" xr2:uid="{8CC6B35D-15F8-46B2-8EDB-45E5A707818B}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate_scenarios" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="83">
   <si>
     <t>status</t>
   </si>
@@ -270,6 +270,21 @@
   </si>
   <si>
     <t>For reference only. This scenario is included in calculator under "Basic Microsoft Foundry Chat"</t>
+  </si>
+  <si>
+    <t>Submitted on 4/1</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/web-apps/guides/enterprise-app-patterns/reliable-web-app/dotnet/guidance</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/example-scenario/apps/scalable-apps-performance-modeling-site-reliability</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/a8aa90b9851f434885cc7a322c96c36b</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/fe330064f12845cf82272f0e803b77e1</t>
   </si>
 </sst>
 </file>
@@ -1131,13 +1146,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1F846C-8C34-46B3-86FF-223EECDE71CC}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.6328125" customWidth="1"/>
     <col min="2" max="2" width="120.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="66.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="150.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -1248,6 +1263,9 @@
       <c r="C8" t="s">
         <v>39</v>
       </c>
+      <c r="D8" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -1259,6 +1277,9 @@
       <c r="C9" t="s">
         <v>40</v>
       </c>
+      <c r="D9" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
@@ -1270,6 +1291,9 @@
       <c r="C10" t="s">
         <v>41</v>
       </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -1281,6 +1305,9 @@
       <c r="C11" t="s">
         <v>43</v>
       </c>
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -1292,6 +1319,9 @@
       <c r="C12" t="s">
         <v>44</v>
       </c>
+      <c r="D12" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
@@ -1303,6 +1333,9 @@
       <c r="C13" t="s">
         <v>46</v>
       </c>
+      <c r="D13" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
@@ -1314,6 +1347,9 @@
       <c r="C14" t="s">
         <v>63</v>
       </c>
+      <c r="D14" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -1325,6 +1361,9 @@
       <c r="C15" t="s">
         <v>49</v>
       </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -1336,6 +1375,9 @@
       <c r="C16" t="s">
         <v>50</v>
       </c>
+      <c r="D16" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
@@ -1347,6 +1389,9 @@
       <c r="C17" t="s">
         <v>51</v>
       </c>
+      <c r="D17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
@@ -1358,6 +1403,9 @@
       <c r="C18" t="s">
         <v>53</v>
       </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
@@ -1369,6 +1417,9 @@
       <c r="C19" t="s">
         <v>54</v>
       </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
@@ -1380,6 +1431,9 @@
       <c r="C20" t="s">
         <v>55</v>
       </c>
+      <c r="D20" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
@@ -1391,6 +1445,9 @@
       <c r="C21" t="s">
         <v>56</v>
       </c>
+      <c r="D21" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
@@ -1402,6 +1459,9 @@
       <c r="C22" t="s">
         <v>57</v>
       </c>
+      <c r="D22" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
@@ -1413,6 +1473,9 @@
       <c r="C23" t="s">
         <v>44</v>
       </c>
+      <c r="D23" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
@@ -1424,6 +1487,9 @@
       <c r="C24" t="s">
         <v>59</v>
       </c>
+      <c r="D24" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
@@ -1434,6 +1500,9 @@
       </c>
       <c r="C25" t="s">
         <v>60</v>
+      </c>
+      <c r="D25" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1446,6 +1515,9 @@
       <c r="C26" t="s">
         <v>48</v>
       </c>
+      <c r="D26" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
@@ -1516,7 +1588,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>2</v>
       </c>
@@ -1527,7 +1599,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>2</v>
       </c>
@@ -1536,6 +1608,34 @@
       </c>
       <c r="C34" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/estimate_scenarios.xlsx
+++ b/estimate_scenarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\v-minasyanva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30700167-AB41-4F56-BFE8-CF7DA68F6E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDD8663-4EA6-4D4F-8DD1-E438D58DBEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38505" yWindow="2565" windowWidth="24630" windowHeight="16680" xr2:uid="{8CC6B35D-15F8-46B2-8EDB-45E5A707818B}"/>
+    <workbookView xWindow="34920" yWindow="1080" windowWidth="22680" windowHeight="18045" xr2:uid="{8CC6B35D-15F8-46B2-8EDB-45E5A707818B}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate_scenarios" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="72">
   <si>
     <t>status</t>
   </si>
@@ -113,9 +113,6 @@
     <t>https://learn.microsoft.com/en-us/azure/architecture/example-scenario/data/small-medium-data-warehouse</t>
   </si>
   <si>
-    <t xml:space="preserve">https://learn.microsoft.com/en-us/azure/architecture/hybrid/hybrid-perf-monitoring </t>
-  </si>
-  <si>
     <t>https://learn.microsoft.com/en-us/azure/architecture/example-scenario/mainframe/reengineer-mainframe-batch-apps-azure</t>
   </si>
   <si>
@@ -131,21 +128,12 @@
     <t>Skip</t>
   </si>
   <si>
-    <t>Submitted on 2/09</t>
-  </si>
-  <si>
-    <t>Submitted on 2/10</t>
-  </si>
-  <si>
     <t>https://learn.microsoft.com/en-us/azure/architecture/example-scenario/networking/split-brain-dns</t>
   </si>
   <si>
     <t>https://learn.microsoft.com/en-us/azure/architecture/ai-ml/architecture/basic-microsoft-foundry-chat</t>
   </si>
   <si>
-    <t xml:space="preserve">https://learn.microsoft.com/en-us/azure/architecture/reference-architectures/containers/aks-microservices/aks-microservices </t>
-  </si>
-  <si>
     <t>estimate_link</t>
   </si>
   <si>
@@ -200,18 +188,12 @@
     <t>https://azure.com/e/4f044f65e46f40c7a9d7a4837a17e6d7</t>
   </si>
   <si>
-    <t>https://azure.microsoft.com/pricing/calculator/?service=monitor</t>
-  </si>
-  <si>
     <t>https://azure.com/e/0bf78de2bf3b45aa961e0dc2f57eb2fe</t>
   </si>
   <si>
     <t>https://azure.com/e/2554c32b19c24b3d9f90d2a73683bd6a</t>
   </si>
   <si>
-    <t>https://azure.microsoft.com/pricing/calculator/?service=kubernetes-service</t>
-  </si>
-  <si>
     <t>https://azure.com/e/149812331b124489ad0ae69e1ad3b118</t>
   </si>
   <si>
@@ -233,15 +215,9 @@
     <t>https://azure.microsoft.com/pricing/calculator/?shared-estimate=61029210b61b4cce8602cb905d7c0dda</t>
   </si>
   <si>
-    <t>Update submitted on 3/2</t>
-  </si>
-  <si>
     <t>https://azure.com/e/b7574e1a2952486e94073601a26ad52f</t>
   </si>
   <si>
-    <t>New estimate link</t>
-  </si>
-  <si>
     <t>https://azure.com/e/b00c1854756f4687a4fcbe0916951aba</t>
   </si>
   <si>
@@ -251,18 +227,12 @@
     <t>https://azure.com/e/16fc0fecb81e49ddadc91f2a0d0ecffc</t>
   </si>
   <si>
-    <t>Submitted on 3/2</t>
-  </si>
-  <si>
     <t>https://learn.microsoft.com/en-us/azure/architecture/reference-architectures/containers/aks-multi-region/aks-multi-cluster</t>
   </si>
   <si>
     <t>https://azure.com/e/2e3a4a64be264e8781f719bbd194e904</t>
   </si>
   <si>
-    <t>New scenario with an estimate</t>
-  </si>
-  <si>
     <t>https://learn.microsoft.com/en-us/azure/architecture/web-apps/app-service/architectures/baseline-zone-redundant</t>
   </si>
   <si>
@@ -270,9 +240,6 @@
   </si>
   <si>
     <t>For reference only. This scenario is included in calculator under "Basic Microsoft Foundry Chat"</t>
-  </si>
-  <si>
-    <t>Submitted on 4/1</t>
   </si>
   <si>
     <t>https://learn.microsoft.com/en-us/azure/architecture/web-apps/guides/enterprise-app-patterns/reliable-web-app/dotnet/guidance</t>
@@ -608,7 +575,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -723,6 +690,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="8"/>
+      </right>
+      <top style="thin">
+        <color theme="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -768,9 +746,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1146,12 +1125,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1F846C-8C34-46B3-86FF-223EECDE71CC}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.6328125" customWidth="1"/>
-    <col min="2" max="2" width="120.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="66.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.54296875" customWidth="1"/>
+    <col min="3" max="3" width="66.54296875" customWidth="1"/>
     <col min="4" max="4" width="29.54296875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1163,479 +1142,376 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
         <v>27</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
         <v>50</v>
       </c>
-      <c r="D16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" t="s">
         <v>51</v>
       </c>
-      <c r="D17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
         <v>53</v>
       </c>
-      <c r="D18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" t="s">
         <v>54</v>
-      </c>
-      <c r="D19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>2</v>
-      </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>2</v>
-      </c>
-      <c r="B30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>2</v>
-      </c>
-      <c r="B31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>2</v>
-      </c>
-      <c r="B32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>2</v>
-      </c>
-      <c r="B34" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" t="s">
-        <v>80</v>
-      </c>
-      <c r="C36" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/estimate_scenarios.xlsx
+++ b/estimate_scenarios.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\v-minasyanva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDD8663-4EA6-4D4F-8DD1-E438D58DBEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9687DB0-95E0-4E01-9574-D426908EA938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34920" yWindow="1080" windowWidth="22680" windowHeight="18045" xr2:uid="{8CC6B35D-15F8-46B2-8EDB-45E5A707818B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{8CC6B35D-15F8-46B2-8EDB-45E5A707818B}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate_scenarios" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">estimate_scenarios!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">estimate_scenarios!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="140">
   <si>
     <t>status</t>
   </si>
@@ -252,6 +253,210 @@
   </si>
   <si>
     <t>https://azure.com/e/fe330064f12845cf82272f0e803b77e1</t>
+  </si>
+  <si>
+    <t>primary_image_path</t>
+  </si>
+  <si>
+    <t>docs/ai-ml/architecture/_images/baseline-microsoft-foundry.svg</t>
+  </si>
+  <si>
+    <t>Build Microsoft Foundry chat</t>
+  </si>
+  <si>
+    <t>Basic Microsoft Foundry Chat</t>
+  </si>
+  <si>
+    <t>Index File Metadata with Azure AI Search</t>
+  </si>
+  <si>
+    <t>Build a document generation system</t>
+  </si>
+  <si>
+    <t>Extract and Map Data from Unstructured Content</t>
+  </si>
+  <si>
+    <t>Build a multi-agent workflow automation solution</t>
+  </si>
+  <si>
+    <t>Build a Knowledge Mining Solution with Azure AI</t>
+  </si>
+  <si>
+    <t>Design an enterprise BI solution</t>
+  </si>
+  <si>
+    <t>Migrate a web app by using Azure API Management</t>
+  </si>
+  <si>
+    <t>Deploy IBM Maximo Application Suite (MAS) on Azure</t>
+  </si>
+  <si>
+    <t>Securely managed web applications </t>
+  </si>
+  <si>
+    <t>Scalable Cloud Applications and SRE</t>
+  </si>
+  <si>
+    <t>Data warehousing and analytics</t>
+  </si>
+  <si>
+    <t>Modern Data Warehouses for SMBs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build a multitier web application </t>
+  </si>
+  <si>
+    <t>Azure API Management Landing Zone Architecture</t>
+  </si>
+  <si>
+    <t>Re-engineer mainframe batch applications on Azure</t>
+  </si>
+  <si>
+    <t>Rehost Information Management System on Azure</t>
+  </si>
+  <si>
+    <t>Siemens Teamcenter baseline architecture on Azure</t>
+  </si>
+  <si>
+    <t>Build a real-time monitoring and observable system</t>
+  </si>
+  <si>
+    <t>A split-brain DNS configuration for a web app</t>
+  </si>
+  <si>
+    <t>Deploy Microservices to Azure Container Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimize your cloud governance  </t>
+  </si>
+  <si>
+    <t>Virtual WAN optimized for secuirty and performance</t>
+  </si>
+  <si>
+    <t>Implement TIC 3.0 compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud-native apps on Kubernetes </t>
+  </si>
+  <si>
+    <t>Run microservices on Azure Kubernetes Service</t>
+  </si>
+  <si>
+    <t>AKS baseline for multiregion clusters</t>
+  </si>
+  <si>
+    <t>IBM Sterling Order Management Software on Azure</t>
+  </si>
+  <si>
+    <t>Baseline highly available zone-redundant web app</t>
+  </si>
+  <si>
+    <t>Basic Web Application</t>
+  </si>
+  <si>
+    <t>Reliable Web App Pattern for .NET</t>
+  </si>
+  <si>
+    <t>Improve web apps security</t>
+  </si>
+  <si>
+    <t>title_in_calculator</t>
+  </si>
+  <si>
+    <t>docs/ai-ml/architecture/_images/openai-end-to-end-basic.svg</t>
+  </si>
+  <si>
+    <t>docs/ai-ml/architecture/_images/search-blob-metadata.png</t>
+  </si>
+  <si>
+    <t>docs/ai-ml/idea/_images/generate-documents.svg</t>
+  </si>
+  <si>
+    <t>docs/ai-ml/idea/_images/multi-modal-content-processing.svg</t>
+  </si>
+  <si>
+    <t>docs/ai-ml/idea/_images/multiple-agent-workflow-automation.svg</t>
+  </si>
+  <si>
+    <t>docs/ai-ml/idea/_images/unlock-insights-from-conversational-data.svg</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/analytics/media/enterprise-bi-scoped-architecture.svg</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/apps/media/api-management-api-scenario-architecture.svg</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/apps/media/deploy-ibm-maximo-application-suite-architecture.svg</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/apps/media/fully-managed-secure-apps.svg</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/apps/media/scalable-apps-performance-modeling-site-reliability.svg</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/data/media/architecture-data-warehousing.svg</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/data/media/small-medium-data-warehouse/small-medium-data-warehouse.svg</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/infrastructure/media/architecture-disaster-recovery-multi-tier-app.svg</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/integration/media/app-gateway-internal-api-management-function.svg</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/mainframe/media/azure-reengineered-mainframe-batch-application-architecture.svg</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/mainframe/media/rehost-ims-raincode-imsql.svg</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/manufacturing/media/teamcenter-baseline-architecture.svg</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/monitoring/media/monitor-media.svg</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/networking/media/split-brain-dns.svg</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/serverless/media/microservices-with-container-apps.svg</t>
+  </si>
+  <si>
+    <t>docs/landing-zones/images/azure-governance-visualizer-accelerator-architecture.svg</t>
+  </si>
+  <si>
+    <t>docs/networking/architecture/_images/performance-security-optimized-vwan-azure.png</t>
+  </si>
+  <si>
+    <t>docs/networking/architecture/_images/trusted-internet-connections.png</t>
+  </si>
+  <si>
+    <t>docs/reference-architectures/containers/aks/images/aks-baseline-architecture.svg</t>
+  </si>
+  <si>
+    <t>docs/reference-architectures/containers/aks-microservices/images/aks-microservices-advanced-production-deployment.svg</t>
+  </si>
+  <si>
+    <t>docs/reference-architectures/containers/aks-multi-region/images/aks-ingress-flow.svg</t>
+  </si>
+  <si>
+    <t>docs/reference-architectures/ibm/media/deploy-ibm-sterling-oms-architecture.svg</t>
+  </si>
+  <si>
+    <t>docs/web-apps/app-service/_images/baseline-app-service-architecture.svg</t>
+  </si>
+  <si>
+    <t>docs/web-apps/app-service/_images/basic-app-service-architecture-flow.svg</t>
+  </si>
+  <si>
+    <t>docs/web-apps/guides/_images/reliable-web-app-dotnet.svg</t>
+  </si>
+  <si>
+    <t>docs/web-apps/guides/_images/multitenant-web-apps.svg</t>
   </si>
 </sst>
 </file>
@@ -746,10 +951,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1125,399 +1331,605 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1F846C-8C34-46B3-86FF-223EECDE71CC}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.6328125" customWidth="1"/>
-    <col min="2" max="2" width="33.54296875" customWidth="1"/>
-    <col min="3" max="3" width="66.54296875" customWidth="1"/>
-    <col min="4" max="4" width="29.54296875" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="120.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.54296875" customWidth="1"/>
+    <col min="5" max="5" width="75.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
       <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>2</v>
       </c>
       <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
       <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>2</v>
       </c>
       <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
         <v>6</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>2</v>
       </c>
       <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>2</v>
       </c>
       <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2</v>
       </c>
       <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>2</v>
       </c>
       <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
         <v>69</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>2</v>
       </c>
       <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>2</v>
       </c>
       <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
         <v>24</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>2</v>
       </c>
       <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
         <v>8</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>2</v>
       </c>
       <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
         <v>13</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>2</v>
       </c>
       <c r="B18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" t="s">
         <v>25</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>2</v>
       </c>
       <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
         <v>26</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E19" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>2</v>
       </c>
       <c r="B20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" t="s">
         <v>27</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>2</v>
       </c>
       <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
         <v>9</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>2</v>
       </c>
       <c r="B22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" t="s">
         <v>30</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E22" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>2</v>
       </c>
       <c r="B23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" t="s">
         <v>18</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>2</v>
       </c>
       <c r="B24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" t="s">
         <v>10</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E24" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>2</v>
       </c>
       <c r="B25" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" t="s">
         <v>28</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>2</v>
       </c>
       <c r="B26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" t="s">
         <v>21</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E26" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>2</v>
       </c>
       <c r="B27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" t="s">
         <v>11</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E27" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>2</v>
       </c>
       <c r="B28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" t="s">
         <v>12</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E28" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>2</v>
       </c>
       <c r="B29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" t="s">
         <v>63</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E29" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>2</v>
       </c>
       <c r="B30" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" t="s">
         <v>20</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E30" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>2</v>
       </c>
       <c r="B31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" t="s">
         <v>65</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E31" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>2</v>
       </c>
       <c r="B32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" t="s">
         <v>14</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>2</v>
       </c>
       <c r="B33" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" t="s">
         <v>68</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E33" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>2</v>
       </c>
       <c r="B34" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" t="s">
         <v>56</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>54</v>
       </c>
+      <c r="E34" t="s">
+        <v>139</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{1C1F846C-8C34-46B3-86FF-223EECDE71CC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D33">
-      <sortCondition ref="D1"/>
+  <autoFilter ref="A1:F1" xr:uid="{1C1F846C-8C34-46B3-86FF-223EECDE71CC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F34">
+      <sortCondition ref="C1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/estimate_scenarios.xlsx
+++ b/estimate_scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\v-minasyanva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFF68CA-488A-413D-9386-E6EB656149FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7EDB39-A39D-4E13-A0E5-959D0C60C979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33720" yWindow="1020" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -788,7 +788,7 @@
     <t>ea009520ea02a043ca8684f3610834813f1e7407fda887c4519122c7d0fdcc9b</t>
   </si>
   <si>
-    <t>https://learn.microsoft.com/en-us/azure/architecture/example-scenario/certificate-lifecycle/index</t>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/example-scenario/certificate-lifecycle</t>
   </si>
 </sst>
 </file>

--- a/estimate_scenarios.xlsx
+++ b/estimate_scenarios.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\v-minasyanva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7EDB39-A39D-4E13-A0E5-959D0C60C979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD030F56-EB39-4FE0-8BB8-983934DF649C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="1020" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="253">
   <si>
     <t>status</t>
   </si>
@@ -43,21 +56,6 @@
     <t>Published</t>
   </si>
   <si>
-    <t>A split-brain DNS configuration for a web app</t>
-  </si>
-  <si>
-    <t>https://learn.microsoft.com/en-us/azure/architecture/example-scenario/networking/split-brain-dns</t>
-  </si>
-  <si>
-    <t>https://azure.com/e/e0b74472f72d48ce891b08b3af105872</t>
-  </si>
-  <si>
-    <t>docs/example-scenario/networking/media/split-brain-dns.svg</t>
-  </si>
-  <si>
-    <t>9f8a29c0463a51e4b4fcbaaa97d6a3a8548ba7853c3aef4f6717005a9082a849</t>
-  </si>
-  <si>
     <t>Advanced AKS microservices architecture</t>
   </si>
   <si>
@@ -70,24 +68,15 @@
     <t>docs/reference-architectures/containers/aks-microservices/images/aks-microservices-advanced-production-deployment.svg</t>
   </si>
   <si>
-    <t>ee8605f73e9d22089322bd291d0347fb330fd407488c4ef1063aa2a122f2c65f</t>
-  </si>
-  <si>
     <t>AKS baseline for multiregion clusters</t>
   </si>
   <si>
     <t>https://learn.microsoft.com/en-us/azure/architecture/reference-architectures/containers/aks-multi-region/aks-multi-cluster</t>
   </si>
   <si>
-    <t>https://azure.com/e/2e3a4a64be264e8781f719bbd194e904</t>
-  </si>
-  <si>
     <t>docs/reference-architectures/containers/aks-multi-region/images/aks-ingress-flow.svg</t>
   </si>
   <si>
-    <t>301a9fb6b28c726a27306d8a8cad7c2a1ffecd393f06a49eea771f224ea6476c</t>
-  </si>
-  <si>
     <t>Analytics End-to-End with Microsoft Fabric</t>
   </si>
   <si>
@@ -100,9 +89,6 @@
     <t>docs/example-scenario/dataplate2e/media/azure-analytics-end-to-end.svg</t>
   </si>
   <si>
-    <t>a434b48923d1c84ec06e8ccd762b65dd4fa653beaea7932f0c836949a5ab3cc4</t>
-  </si>
-  <si>
     <t>Automate Document Classification in Azure</t>
   </si>
   <si>
@@ -115,9 +101,6 @@
     <t>docs/ai-ml/architecture/_images/automate-document-classification-durable-functions.svg</t>
   </si>
   <si>
-    <t>350331b5d7cea95ecb155c6c7190d2e761f6d595f3d3b26a8ef853b41a75d55c</t>
-  </si>
-  <si>
     <t>Automate PDF forms processing</t>
   </si>
   <si>
@@ -130,9 +113,6 @@
     <t>docs/ai-ml/architecture/_images/automate-pdf-forms-processing.png</t>
   </si>
   <si>
-    <t>ebaa0835a65ccd85457670b5c167361a8de6f933fe8c5344a94d1c32750a1e49</t>
-  </si>
-  <si>
     <t>Azure API Management Landing Zone Architecture</t>
   </si>
   <si>
@@ -143,9 +123,6 @@
   </si>
   <si>
     <t>docs/example-scenario/integration/media/app-gateway-internal-api-management-function.svg</t>
-  </si>
-  <si>
-    <t>16483f7a89674c0d9132732879d5573e4b4a69ffb13326f647793ca810a44801</t>
   </si>
   <si>
     <t>Azure Data Factory in an Azure Landing Zone</t>
@@ -161,9 +138,6 @@
 </t>
   </si>
   <si>
-    <t>6428539c859aa97bb3318bf2c8a2423708c98f46a1242c50a218e7317f65cc23</t>
-  </si>
-  <si>
     <t>Azure Local Baseline Reference Architecture</t>
   </si>
   <si>
@@ -176,9 +150,6 @@
     <t>docs/hybrid/images/azure-local-baseline.png</t>
   </si>
   <si>
-    <t>da1d451945e5984b01ed152a1d713591878e60293f08aaed0363156dad087408</t>
-  </si>
-  <si>
     <t>Azure Virtual Desktop for Azure Local</t>
   </si>
   <si>
@@ -191,9 +162,6 @@
     <t>docs/hybrid/images/azure-virtual-desktop-azure-local.svg</t>
   </si>
   <si>
-    <t>c09ab48dfb1dd468a821e38e3c029edc1b64cb5527b3271a3295b74c39ec5b40</t>
-  </si>
-  <si>
     <t>Azure Virtual Machines baseline architecture</t>
   </si>
   <si>
@@ -206,9 +174,6 @@
     <t>docs/virtual-machines/media/baseline-architecture.svg</t>
   </si>
   <si>
-    <t>0b7a0d3139ffefdac15a11186ef0dee20f3fa6fa240bc642dc0eea5dcd5a1fd9</t>
-  </si>
-  <si>
     <t>Baseline Architecture for an AKS Cluster</t>
   </si>
   <si>
@@ -221,9 +186,6 @@
     <t>docs/reference-architectures/containers/aks/images/aks-baseline-architecture.svg</t>
   </si>
   <si>
-    <t>b3b7bd4d2524e3794a5710d02e63ac647b608fc74f4418a3fd8c61bd6f9e1e64</t>
-  </si>
-  <si>
     <t>Baseline highly available zone-redundant web app</t>
   </si>
   <si>
@@ -236,9 +198,6 @@
     <t>docs/web-apps/app-service/_images/baseline-app-service-architecture.svg</t>
   </si>
   <si>
-    <t>a99a630ba3c080f45a3f43f25ad88a774ddadd646c7f5b466f4eca01ec33e23e</t>
-  </si>
-  <si>
     <t>Skip</t>
   </si>
   <si>
@@ -266,9 +225,6 @@
     <t>docs/web-apps/app-service/_images/basic-app-service-architecture-flow.svg</t>
   </si>
   <si>
-    <t>e2bbe9263b76cb174cf3bdbb81297f0f10d997d9f0556ff20846e3daf255fcb7</t>
-  </si>
-  <si>
     <t>Build a Knowledge Mining Solution with Azure AI</t>
   </si>
   <si>
@@ -281,9 +237,6 @@
     <t>docs/ai-ml/idea/_images/unlock-insights-from-conversational-data.svg</t>
   </si>
   <si>
-    <t>7adb12fa8666af4616ae27baa6a82c4b607a4fe598023b59d4c24f6bf3e5cb1a</t>
-  </si>
-  <si>
     <t>Build a multi-agent workflow automation solution</t>
   </si>
   <si>
@@ -296,9 +249,6 @@
     <t>docs/ai-ml/idea/_images/multiple-agent-workflow-automation.svg</t>
   </si>
   <si>
-    <t>d8cc188ab174840a058d35fb73fe57ae2e08459f77ae3526296d340abb458f17</t>
-  </si>
-  <si>
     <t xml:space="preserve">Build a multitier web application </t>
   </si>
   <si>
@@ -311,9 +261,6 @@
     <t>docs/example-scenario/infrastructure/media/architecture-disaster-recovery-multi-tier-app.svg</t>
   </si>
   <si>
-    <t>a8a8915ffd6c38b8c9cdb32e6bfb288dc3ebd2dd1e51685d68973317df24fdd6</t>
-  </si>
-  <si>
     <t>Build a real-time monitoring and observable system</t>
   </si>
   <si>
@@ -326,9 +273,6 @@
     <t>docs/example-scenario/monitoring/media/monitor-media.svg</t>
   </si>
   <si>
-    <t>8eef10d4523550fe0250d6fcc6bbb8dd4a5a0f9720a4be043d709aab2c9828ce</t>
-  </si>
-  <si>
     <t>Build Microsoft Foundry chat</t>
   </si>
   <si>
@@ -341,9 +285,6 @@
     <t>docs/ai-ml/architecture/_images/baseline-microsoft-foundry.svg</t>
   </si>
   <si>
-    <t>d413aea4bcb6a6a5650a17a377f62bf5df656a6da417f5c39cf389dc5af7331b</t>
-  </si>
-  <si>
     <t>Certificate Life Cycle Management on Azure</t>
   </si>
   <si>
@@ -353,9 +294,6 @@
     <t>docs/example-scenario/certificate-lifecycle/media/certificate-life-cycle-architecture.svg</t>
   </si>
   <si>
-    <t>36f6e1af5bdc5c901bc1ae79f5d29aea505033e5cbc73cb135ac6c0030901306</t>
-  </si>
-  <si>
     <t>Connect an On-Premises Network to Azure</t>
   </si>
   <si>
@@ -368,9 +306,6 @@
     <t>docs/reference-architectures/hybrid-networking/images/expressroute-vpn-failover.svg</t>
   </si>
   <si>
-    <t>97d1082c8bd902e9072ca05ac4dc3c00c167147050c16bcf9eefb149ea70f551</t>
-  </si>
-  <si>
     <t>Data warehousing and analytics</t>
   </si>
   <si>
@@ -383,9 +318,6 @@
     <t>docs/example-scenario/data/media/architecture-data-warehousing.svg</t>
   </si>
   <si>
-    <t>218b19439b5373be100fb5713422948361c3934ae17452f084093cb2c31ea68a</t>
-  </si>
-  <si>
     <t>Deploy IBM Maximo Application Suite (MAS) on Azure</t>
   </si>
   <si>
@@ -398,9 +330,6 @@
     <t>docs/example-scenario/apps/media/deploy-ibm-maximo-application-suite-architecture.svg</t>
   </si>
   <si>
-    <t>ddaac07e8358e53c0397cc83465474dfd692f3e957569cea6edc2a37d1cbdaa8</t>
-  </si>
-  <si>
     <t>Deploy Microservices to Azure Container Apps</t>
   </si>
   <si>
@@ -413,9 +342,6 @@
     <t>docs/example-scenario/serverless/media/microservices-with-container-apps.svg</t>
   </si>
   <si>
-    <t>4473416f570d78737c2cf65bb879f34a8587338eddacf67372e343ff0b266d01</t>
-  </si>
-  <si>
     <t>Design a polyglot persistence data solution</t>
   </si>
   <si>
@@ -428,9 +354,6 @@
     <t>docs/databases/idea/images/combine-relational-nosql/solution-diagram.svg</t>
   </si>
   <si>
-    <t>7b5e075623b293fb48f0473cb634c816a875772f612b601c63c33e36efddbbbc</t>
-  </si>
-  <si>
     <t>Design an enterprise BI solution</t>
   </si>
   <si>
@@ -443,9 +366,6 @@
     <t>docs/example-scenario/analytics/media/enterprise-bi-scoped-architecture.svg</t>
   </si>
   <si>
-    <t>2401e78481a4565a8dda0704d638d576ee46698e5fe6370bd27d37c2cad3a11a</t>
-  </si>
-  <si>
     <t>Disaster recovery for an Azure Data Platform</t>
   </si>
   <si>
@@ -458,9 +378,6 @@
     <t>docs/data-guide/images/dr-for-azure-data-platform-landing-zone-architecture.svg</t>
   </si>
   <si>
-    <t>3ec94221f14ba6d4209d5ec3b4334c32813beb682085657c52b8475002e90d67</t>
-  </si>
-  <si>
     <t>Extract and Map Data from Unstructured Content</t>
   </si>
   <si>
@@ -473,9 +390,6 @@
     <t>docs/ai-ml/idea/_images/multi-modal-content-processing.svg</t>
   </si>
   <si>
-    <t>50cdcc155c7e6d0b4bf0b556309498b4af6140268bbf77032496ea9f19bb6518</t>
-  </si>
-  <si>
     <t>Generate Documents from Your Data</t>
   </si>
   <si>
@@ -488,9 +402,6 @@
     <t>docs/ai-ml/idea/_images/generate-documents.svg</t>
   </si>
   <si>
-    <t>c560e98d718be31ffaf3f2f14a817d8734fdd32e1f637646786d228134e772bd</t>
-  </si>
-  <si>
     <t>Hub-Spoke Network Topology in Azure</t>
   </si>
   <si>
@@ -503,9 +414,6 @@
     <t>docs/networking/architecture/_images/hub-spoke-network-topology-architecture.svg</t>
   </si>
   <si>
-    <t>40fa6c07518922d3bb50e8d2cb06e989baa04ea068bb61c895c0075497d47e97</t>
-  </si>
-  <si>
     <t>Hub-Spoke Network Topology with Virtual WAN</t>
   </si>
   <si>
@@ -518,9 +426,6 @@
     <t>docs/networking/architecture/_images/hub-spoke-virtual-wan-architecture-1.svg</t>
   </si>
   <si>
-    <t>a916c627cb5d322d220b6258519936b54821ff4ba3244e48f4e90192c5470d37</t>
-  </si>
-  <si>
     <t>IBM Sterling Order Management Software on Azure</t>
   </si>
   <si>
@@ -530,9 +435,6 @@
     <t>docs/reference-architectures/ibm/media/deploy-ibm-sterling-oms-architecture.svg</t>
   </si>
   <si>
-    <t>9dc3ea0202a19dda9a554387a30578e99ea4fefd1ad4db9183c45813e66e70a2</t>
-  </si>
-  <si>
     <t>Implement a secure hybrid network</t>
   </si>
   <si>
@@ -545,9 +447,6 @@
     <t>docs/reference-architectures/dmz/images/dmz-private.png</t>
   </si>
   <si>
-    <t>315e585e3693be1fd1681b105addd3dd43c0a2db97c1122b90a55f55a3efb90b</t>
-  </si>
-  <si>
     <t>Implement TIC 3.0 compliance</t>
   </si>
   <si>
@@ -560,9 +459,6 @@
     <t>docs/networking/architecture/_images/trusted-internet-connections.png</t>
   </si>
   <si>
-    <t>6e49a29221833ab0313235c5775e0cd76977e4d6d59c0d89047a740dfaabec56</t>
-  </si>
-  <si>
     <t>Improve web apps security</t>
   </si>
   <si>
@@ -575,9 +471,6 @@
     <t>docs/web-apps/guides/_images/multitenant-web-apps.svg</t>
   </si>
   <si>
-    <t>2a8e7418f056b826a1f00eb6b3198f7c4d74a2261fd3e0aaae13e41c37ab7527</t>
-  </si>
-  <si>
     <t>Index File Metadata with Azure AI Search</t>
   </si>
   <si>
@@ -590,9 +483,6 @@
     <t>docs/ai-ml/architecture/_images/search-blob-metadata.png</t>
   </si>
   <si>
-    <t>293acc9bf8c0cb93e80fa41dcd260b82ebb5495689678c93a26cb3b208922a02</t>
-  </si>
-  <si>
     <t>Microservices Architecture on AKS</t>
   </si>
   <si>
@@ -605,9 +495,6 @@
     <t>docs/reference-architectures/containers/aks-microservices/images/microservices-architecture.svg</t>
   </si>
   <si>
-    <t>afe65947fec6b93f844493c067531e128c8cfbc88ed28def2f4c744538eadfca</t>
-  </si>
-  <si>
     <t>Microsoft Foundry Chat in an Azure Landing Zone</t>
   </si>
   <si>
@@ -620,9 +507,6 @@
     <t>docs/ai-ml/architecture/_images/baseline-microsoft-foundry-landing-zone.svg</t>
   </si>
   <si>
-    <t>627fb3019c65c980e7441daa694b8392ea033523d38c2baefe1d327eeb0c6554</t>
-  </si>
-  <si>
     <t>Migrate a web app by using Azure API Management</t>
   </si>
   <si>
@@ -635,9 +519,6 @@
     <t>docs/example-scenario/apps/media/api-management-api-scenario-architecture.svg</t>
   </si>
   <si>
-    <t>9d867f057bf2fb9248bffb78bab5800618e25f1ea03a377dd00a9887a4b31b2d</t>
-  </si>
-  <si>
     <t>Modern Data Warehouses for SMBs</t>
   </si>
   <si>
@@ -650,9 +531,6 @@
     <t>docs/example-scenario/data/media/small-medium-data-warehouse/small-medium-data-warehouse.svg</t>
   </si>
   <si>
-    <t>72aa5cfe008657e74861b80c995f25afc4d596de5e0612ea97f56a7b3583c19d</t>
-  </si>
-  <si>
     <t>Re-engineer mainframe batch applications on Azure</t>
   </si>
   <si>
@@ -665,9 +543,6 @@
     <t>docs/example-scenario/mainframe/media/azure-reengineered-mainframe-batch-application-architecture.svg</t>
   </si>
   <si>
-    <t>c79c5272a48bb61562b412156d9af517a616f077f10c41594bc2f787073d684d</t>
-  </si>
-  <si>
     <t>Rehost Information Management System on Azure</t>
   </si>
   <si>
@@ -680,9 +555,6 @@
     <t>docs/example-scenario/mainframe/media/rehost-ims-raincode-imsql.svg</t>
   </si>
   <si>
-    <t>1e914245e88ee928f9840d67e17a2b033d65151fe2d26fc0310541e6a6d618cc</t>
-  </si>
-  <si>
     <t>Reliable Web App Pattern for .NET</t>
   </si>
   <si>
@@ -695,9 +567,6 @@
     <t>docs/web-apps/guides/_images/reliable-web-app-dotnet.svg</t>
   </si>
   <si>
-    <t>13c1ebb246df3a2437b878469293835cb3178f0d67ee292c1bbf27bbe3ea9e08</t>
-  </si>
-  <si>
     <t>SAP deployment in Azure using an Oracle database</t>
   </si>
   <si>
@@ -710,9 +579,6 @@
     <t>docs/example-scenario/apps/media/sap-oracle-architecture.png</t>
   </si>
   <si>
-    <t>8d2bf53d50f099215ccb89072ee4ab2b1b18bff104f32b59c78a1bf0749a83b6</t>
-  </si>
-  <si>
     <t>SAP HANA for Linux VMs in Scale-up Systems</t>
   </si>
   <si>
@@ -725,9 +591,6 @@
     <t>docs/reference-architectures/sap/images/sap-hana-architecture.png</t>
   </si>
   <si>
-    <t>fcd6251f40bd87728e560efd4069df617d858697d77fded83daa6fe84f200772</t>
-  </si>
-  <si>
     <t>Scalable Cloud Applications and SRE</t>
   </si>
   <si>
@@ -740,9 +603,6 @@
     <t>docs/example-scenario/apps/media/scalable-apps-performance-modeling-site-reliability.svg</t>
   </si>
   <si>
-    <t>05f3921a952c4196242966495898fa548276ac9426bd70b64e2ef4d04413c7d4</t>
-  </si>
-  <si>
     <t>Securely managed web applications </t>
   </si>
   <si>
@@ -755,9 +615,6 @@
     <t>docs/example-scenario/apps/media/fully-managed-secure-apps.svg</t>
   </si>
   <si>
-    <t>e5d160d9c263181b13d605f58c3d1b47fa509e71ad9e8426d8b9918e12d00e92</t>
-  </si>
-  <si>
     <t>Siemens Teamcenter baseline architecture on Azure</t>
   </si>
   <si>
@@ -770,9 +627,6 @@
     <t>docs/example-scenario/manufacturing/media/teamcenter-baseline-architecture.svg</t>
   </si>
   <si>
-    <t>99b17a470d9fe044a6b8e6882842d53b52e349c672383ebcaaff4fe7bfdb9fb8</t>
-  </si>
-  <si>
     <t>Virtual WAN optimized for secuirty and performance</t>
   </si>
   <si>
@@ -785,10 +639,160 @@
     <t>docs/networking/architecture/_images/performance-security-optimized-vwan-azure.png</t>
   </si>
   <si>
-    <t>ea009520ea02a043ca8684f3610834813f1e7407fda887c4519122c7d0fdcc9b</t>
-  </si>
-  <si>
     <t>https://learn.microsoft.com/en-us/azure/architecture/example-scenario/certificate-lifecycle</t>
+  </si>
+  <si>
+    <t>Submitted for updates</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/97dbd336e7224a9890652d7418be9e4d</t>
+  </si>
+  <si>
+    <t>Submitted a new scenario</t>
+  </si>
+  <si>
+    <t>Build ETL pipelines with Azure Databricks</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/solution-ideas/articles/ingest-etl-stream-with-adb</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/95d70fad3eaf46c48ccbf2f47c271655</t>
+  </si>
+  <si>
+    <t>docs/solution-ideas/media/ingest-etl-and-stream-processing-with-azure-databricks.svg</t>
+  </si>
+  <si>
+    <t>Computer Forensics Chain of Custody in Azure</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/example-scenario/forensics</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/f88a6df49691485aa783bab2d417d034</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/forensics/media/chain-of-custody.svg</t>
+  </si>
+  <si>
+    <t>Custom Document Processing Models on Azure</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/ai-ml/architecture/build-deploy-custom-models</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/a87d001c7a4f49b28939a000899c1eed</t>
+  </si>
+  <si>
+    <t>docs/ai-ml/architecture/_images/build-deploy-custom-models.svg</t>
+  </si>
+  <si>
+    <t>Esri ArcGIS Platform on Azure Virtual Desktop</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/example-scenario/data/esri-arcgis-azure-virtual-desktop</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/ab6a1e4745014c639d4efffb50320941</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/data/media/virtual-desktop-azure-network.svg</t>
+  </si>
+  <si>
+    <t>Extract text from objects using Foundry Tools</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/example-scenario/ai/extract-object-text</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/97bc706f51b14769bc69f9084af3e2e8</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/ai/media/architecture-extract-object-text.svg</t>
+  </si>
+  <si>
+    <t>Greenfield Lakehouse on Microsoft Fabric</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/example-scenario/data/greenfield-lakehouse-fabric</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/2c3bbe1a61044297a4c1db3a2537d44d</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/data/media/greenfield-lakehouse-fabric/greenfield-lakehouse-fabric.svg</t>
+  </si>
+  <si>
+    <t>Modern Analytics Architecture with Azure Databricks</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/solution-ideas/articles/azure-databricks-modern-analytics-architecture</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/6a6901def01b465ba14ed3cef1e3e9d3</t>
+  </si>
+  <si>
+    <t>docs/solution-ideas/media/azure-databricks-modern-analytics-architecture.svg</t>
+  </si>
+  <si>
+    <t>Modern Data Platform Architecture for SMBs</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/solution-ideas/articles/small-medium-modern-data-platform</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/e656290b2a3f499b97ed8dcfaebc5607</t>
+  </si>
+  <si>
+    <t>docs/solution-ideas/media/small-medium-businesses-architecture.svg</t>
+  </si>
+  <si>
+    <t>Real-Time Analytics with Microsoft Fabric</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/solution-ideas/articles/analytics-service-bus</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/72244c05056740bf9244c673a3211b77</t>
+  </si>
+  <si>
+    <t>docs/solution-ideas/media/fabric-real-time-intelligence-service-bus.svg</t>
+  </si>
+  <si>
+    <t>Use AI to Forecast Customer Orders</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/ai-ml/idea/next-order-forecasting</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/037a835bf7494403b19ef3f0d2ad226b</t>
+  </si>
+  <si>
+    <t>docs/ai-ml/idea/_images/next-order-forecasting.svg</t>
+  </si>
+  <si>
+    <t>Use Azure Databricks to Orchestrate MLOps</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/ai-ml/idea/orchestrate-machine-learning-azure-databricks</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/6dd05b9ac79a42ff8f76b1a146ee73eb</t>
+  </si>
+  <si>
+    <t>docs/ai-ml/idea/_images/orchestrate-machine-learning-azure-databricks.svg</t>
+  </si>
+  <si>
+    <t>Use Azure Front Door to Secure AKS Workloads</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/en-us/azure/architecture/example-scenario/aks-front-door/aks-front-door</t>
+  </si>
+  <si>
+    <t>https://azure.com/e/2668dfa253464aecbfed296014f40ff2</t>
+  </si>
+  <si>
+    <t>docs/example-scenario/aks-front-door/media/aks-front-door.svg</t>
   </si>
 </sst>
 </file>
@@ -824,9 +828,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1129,8 +1132,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" customWidth="1"/>
+    <col min="4" max="4" width="23.453125" customWidth="1"/>
+    <col min="5" max="5" width="44.54296875" customWidth="1"/>
+    <col min="6" max="6" width="89.6328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -1154,999 +1165,1039 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>202</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>203</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>206</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>207</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>209</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>211</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>26</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>214</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>215</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>202</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>217</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>218</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>219</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" t="s">
-        <v>41</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>221</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>222</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>223</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>225</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>226</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>227</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>229</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>230</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>231</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>202</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>202</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>202</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E15" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>202</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>202</v>
+      </c>
+      <c r="B18" t="s">
         <v>79</v>
       </c>
-      <c r="E16" t="s">
+      <c r="C18" t="s">
         <v>80</v>
       </c>
-      <c r="F16" t="s">
+      <c r="D18" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="E18" t="s">
         <v>82</v>
       </c>
-      <c r="C17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" t="s">
-        <v>85</v>
-      </c>
-      <c r="F17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" t="s">
-        <v>88</v>
-      </c>
-      <c r="D18" t="s">
-        <v>89</v>
-      </c>
-      <c r="E18" t="s">
-        <v>90</v>
-      </c>
-      <c r="F18" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>233</v>
       </c>
       <c r="C20" t="s">
+        <v>234</v>
+      </c>
+      <c r="D20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E20" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>202</v>
+      </c>
+      <c r="B21" t="s">
         <v>98</v>
       </c>
-      <c r="D20" t="s">
+      <c r="C21" t="s">
         <v>99</v>
       </c>
-      <c r="E20" t="s">
+      <c r="D21" t="s">
         <v>100</v>
       </c>
-      <c r="F20" t="s">
+      <c r="E21" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C21" t="s">
-        <v>103</v>
-      </c>
-      <c r="D21" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" t="s">
-        <v>105</v>
-      </c>
-      <c r="F21" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>255</v>
+        <v>237</v>
+      </c>
+      <c r="C22" t="s">
+        <v>238</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="E22" t="s">
-        <v>109</v>
-      </c>
-      <c r="F22" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>241</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>242</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>114</v>
-      </c>
-      <c r="F23" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>245</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>246</v>
       </c>
       <c r="D24" t="s">
-        <v>118</v>
+        <v>247</v>
       </c>
       <c r="E24" t="s">
-        <v>119</v>
-      </c>
-      <c r="F24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>249</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>250</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>251</v>
       </c>
       <c r="E25" t="s">
-        <v>124</v>
-      </c>
-      <c r="F25" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s">
-        <v>129</v>
-      </c>
-      <c r="F26" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="E27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F27" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>202</v>
       </c>
       <c r="B28" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s">
-        <v>139</v>
-      </c>
-      <c r="F28" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B29" t="s">
-        <v>141</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>142</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>143</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>144</v>
-      </c>
-      <c r="F29" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>202</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="E30" t="s">
-        <v>149</v>
-      </c>
-      <c r="F30" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B31" t="s">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>154</v>
-      </c>
-      <c r="F31" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B32" t="s">
-        <v>156</v>
+        <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>157</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>158</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>159</v>
-      </c>
-      <c r="F32" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>202</v>
       </c>
       <c r="B33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" t="s">
+        <v>120</v>
+      </c>
+      <c r="E33" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>204</v>
+      </c>
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>202</v>
+      </c>
+      <c r="B35" t="s">
         <v>161</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C35" t="s">
         <v>162</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D35" t="s">
         <v>163</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E35" t="s">
         <v>164</v>
       </c>
-      <c r="F33" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" t="s">
-        <v>166</v>
-      </c>
-      <c r="C34" t="s">
-        <v>167</v>
-      </c>
-      <c r="D34" t="s">
-        <v>123</v>
-      </c>
-      <c r="E34" t="s">
-        <v>168</v>
-      </c>
-      <c r="F34" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" t="s">
-        <v>170</v>
-      </c>
-      <c r="C35" t="s">
-        <v>171</v>
-      </c>
-      <c r="D35" t="s">
-        <v>172</v>
-      </c>
-      <c r="E35" t="s">
-        <v>173</v>
-      </c>
-      <c r="F35" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B36" t="s">
-        <v>175</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>176</v>
+        <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>177</v>
+        <v>36</v>
       </c>
       <c r="E36" t="s">
-        <v>178</v>
-      </c>
-      <c r="F36" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B37" t="s">
-        <v>180</v>
+        <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>181</v>
+        <v>39</v>
       </c>
       <c r="D37" t="s">
-        <v>182</v>
+        <v>40</v>
       </c>
       <c r="E37" t="s">
-        <v>183</v>
-      </c>
-      <c r="F37" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B38" t="s">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>186</v>
+        <v>43</v>
       </c>
       <c r="D38" t="s">
-        <v>187</v>
+        <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>188</v>
-      </c>
-      <c r="F38" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="C39" t="s">
-        <v>191</v>
+        <v>131</v>
       </c>
       <c r="D39" t="s">
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="E39" t="s">
-        <v>193</v>
-      </c>
-      <c r="F39" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B40" t="s">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="C40" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D40" t="s">
-        <v>197</v>
+        <v>84</v>
       </c>
       <c r="E40" t="s">
-        <v>198</v>
-      </c>
-      <c r="F40" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>200</v>
+        <v>137</v>
       </c>
       <c r="C41" t="s">
-        <v>201</v>
+        <v>138</v>
       </c>
       <c r="D41" t="s">
-        <v>202</v>
+        <v>139</v>
       </c>
       <c r="E41" t="s">
-        <v>203</v>
-      </c>
-      <c r="F41" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>205</v>
+        <v>141</v>
       </c>
       <c r="C42" t="s">
-        <v>206</v>
+        <v>142</v>
       </c>
       <c r="D42" t="s">
-        <v>207</v>
+        <v>143</v>
       </c>
       <c r="E42" t="s">
-        <v>208</v>
-      </c>
-      <c r="F42" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>210</v>
+        <v>145</v>
       </c>
       <c r="C43" t="s">
-        <v>211</v>
+        <v>146</v>
       </c>
       <c r="D43" t="s">
-        <v>212</v>
+        <v>147</v>
       </c>
       <c r="E43" t="s">
-        <v>213</v>
-      </c>
-      <c r="F43" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B44" t="s">
-        <v>215</v>
+        <v>86</v>
       </c>
       <c r="C44" t="s">
-        <v>216</v>
+        <v>87</v>
       </c>
       <c r="D44" t="s">
-        <v>217</v>
+        <v>88</v>
       </c>
       <c r="E44" t="s">
-        <v>218</v>
-      </c>
-      <c r="F44" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B45" t="s">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="C45" t="s">
-        <v>221</v>
+        <v>103</v>
       </c>
       <c r="D45" t="s">
-        <v>222</v>
+        <v>104</v>
       </c>
       <c r="E45" t="s">
-        <v>223</v>
-      </c>
-      <c r="F45" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>225</v>
+        <v>157</v>
       </c>
       <c r="C46" t="s">
-        <v>226</v>
+        <v>158</v>
       </c>
       <c r="D46" t="s">
-        <v>227</v>
+        <v>159</v>
       </c>
       <c r="E46" t="s">
-        <v>228</v>
-      </c>
-      <c r="F46" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B47" t="s">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="C47" t="s">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="D47" t="s">
-        <v>232</v>
+        <v>112</v>
       </c>
       <c r="E47" t="s">
-        <v>233</v>
-      </c>
-      <c r="F47" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B48" t="s">
-        <v>235</v>
+        <v>122</v>
       </c>
       <c r="C48" t="s">
-        <v>236</v>
+        <v>123</v>
       </c>
       <c r="D48" t="s">
-        <v>237</v>
+        <v>124</v>
       </c>
       <c r="E48" t="s">
-        <v>238</v>
-      </c>
-      <c r="F48" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>6</v>
+        <v>202</v>
       </c>
       <c r="B49" t="s">
-        <v>240</v>
+        <v>193</v>
       </c>
       <c r="C49" t="s">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="D49" t="s">
-        <v>242</v>
+        <v>195</v>
       </c>
       <c r="E49" t="s">
-        <v>243</v>
-      </c>
-      <c r="F49" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="B50" t="s">
-        <v>245</v>
+        <v>126</v>
       </c>
       <c r="C50" t="s">
-        <v>246</v>
+        <v>127</v>
       </c>
       <c r="D50" t="s">
-        <v>247</v>
+        <v>128</v>
       </c>
       <c r="E50" t="s">
-        <v>248</v>
-      </c>
-      <c r="F50" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>6</v>
       </c>
       <c r="B51" t="s">
-        <v>250</v>
+        <v>165</v>
       </c>
       <c r="C51" t="s">
-        <v>251</v>
+        <v>166</v>
       </c>
       <c r="D51" t="s">
-        <v>252</v>
+        <v>167</v>
       </c>
       <c r="E51" t="s">
-        <v>253</v>
-      </c>
-      <c r="F51" t="s">
-        <v>254</v>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" t="s">
+        <v>169</v>
+      </c>
+      <c r="C52" t="s">
+        <v>170</v>
+      </c>
+      <c r="D52" t="s">
+        <v>171</v>
+      </c>
+      <c r="E52" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" t="s">
+        <v>174</v>
+      </c>
+      <c r="D53" t="s">
+        <v>175</v>
+      </c>
+      <c r="E53" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>204</v>
+      </c>
+      <c r="B54" t="s">
+        <v>133</v>
+      </c>
+      <c r="C54" t="s">
+        <v>134</v>
+      </c>
+      <c r="D54" t="s">
+        <v>135</v>
+      </c>
+      <c r="E54" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>204</v>
+      </c>
+      <c r="B55" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" t="s">
+        <v>150</v>
+      </c>
+      <c r="D55" t="s">
+        <v>151</v>
+      </c>
+      <c r="E55" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" t="s">
+        <v>185</v>
+      </c>
+      <c r="C56" t="s">
+        <v>186</v>
+      </c>
+      <c r="D56" t="s">
+        <v>187</v>
+      </c>
+      <c r="E56" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" t="s">
+        <v>189</v>
+      </c>
+      <c r="C57" t="s">
+        <v>190</v>
+      </c>
+      <c r="D57" t="s">
+        <v>191</v>
+      </c>
+      <c r="E57" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>202</v>
+      </c>
+      <c r="B58" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>204</v>
+      </c>
+      <c r="B59" t="s">
+        <v>153</v>
+      </c>
+      <c r="C59" t="s">
+        <v>154</v>
+      </c>
+      <c r="D59" t="s">
+        <v>155</v>
+      </c>
+      <c r="E59" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>204</v>
+      </c>
+      <c r="B60" t="s">
+        <v>177</v>
+      </c>
+      <c r="C60" t="s">
+        <v>178</v>
+      </c>
+      <c r="D60" t="s">
+        <v>179</v>
+      </c>
+      <c r="E60" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>204</v>
+      </c>
+      <c r="B61" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61" t="s">
+        <v>182</v>
+      </c>
+      <c r="D61" t="s">
+        <v>183</v>
+      </c>
+      <c r="E61" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" t="s">
+        <v>197</v>
+      </c>
+      <c r="C62" t="s">
+        <v>198</v>
+      </c>
+      <c r="D62" t="s">
+        <v>199</v>
+      </c>
+      <c r="E62" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
